--- a/backend/Attendance_Reports/Master_Attendance_Computer Science_3rd Year_A.xlsx
+++ b/backend/Attendance_Reports/Master_Attendance_Computer Science_3rd Year_A.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,61 @@
           <t>2026-04-06 (ENGLISH)</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-06 (applied maths)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-09 (ENGLISH)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (Test Subject)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (ENGLISH)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (maths)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (science)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 (ENGLISH)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (english)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 (cse)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (Verification Test)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10 (zoology)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,6 +543,61 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Absent</t>
         </is>
       </c>
@@ -495,7 +605,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23cobea546</t>
+          <t>23COBEA546</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,6 +629,61 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -527,7 +692,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23cobea456</t>
+          <t>23COBEA456</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -553,6 +718,140 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Absent</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GQ0953</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>moosa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3rd Year</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Present</t>
         </is>
       </c>
     </row>
